--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_09_Multi-Agent _ A2A Systems/Day_09_Phan_01_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_09_Multi-Agent _ A2A Systems/Day_09_Phan_01_20_Cau.xlsx
@@ -1241,7 +1241,7 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,4,5</t>
         </is>
       </c>
       <c r="I15" s="4" t="n">
@@ -1250,7 +1250,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hành động đòi hỏi kiến thức nghiệp vụ thuộc về worker chuyên trách.</t>
+          <t>Trách nhiệm chuẩn của một supervisor mỏng (thin supervisor) trong kiến trúc multi-agent: (a) Phân loại yêu cầu đầu vào; (b) Lựa chọn worker chuyên trách phù hợp; (d) Theo dõi tiến độ thực thi và xử lý leo thang (escalation); (e) Tổng hợp kết quả cuối cùng có đầy đủ dấu vết truy vết. Supervisor mỏng tuyệt đối không tự ý áp đặt chính sách chuyên ngành thay cho worker.</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I17" s="4" t="n">
@@ -1350,7 +1350,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Bên gọi và worker phải kiểm thử được mà không cần đọc prompt nội bộ.</t>
+          <t>Hợp đồng giao việc (task contract) cho RetrievalWorker cần bao gồm: (a) Nhiệm vụ cụ thể và ngữ cảnh được giới hạn chặt chẽ; (b) Các ràng buộc về phiên bản tài liệu, đối tượng áp dụng; (c) Schema đầu ra có cấu trúc rõ ràng; (d) Ngữ nghĩa và quy ước xử lý khi gặp lỗi hoặc không tìm thấy kết quả. Không được chuyển toàn bộ lịch sử và bí mật người dùng.</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4,5</t>
         </is>
       </c>
       <c r="I20" s="4" t="n">
@@ -1493,7 +1493,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mỗi field phải có kiểu dữ liệu và ý nghĩa trong vòng đời xử lý.</t>
+          <t>Các trường dữ liệu hợp lệ cho state điều phối có kiểu dữ liệu (strongly typed orchestration state): (a) `task: str`; (b) `retrieved_chunks: list[Chunk]`; (c) `policy_result: PolicyResult | None`; (d) `status: enum`; (e) `final_answer: str | None`. Tuyệt đối không đưa vào trường chứa dump toàn bộ prompt thô không kiểm soát.</t>
         </is>
       </c>
     </row>
